--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Open.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Open.xlsx
@@ -31,7 +31,7 @@
     <t>A*</t>
   </si>
   <si>
-    <t>JPS-BDS-GL-BRC-PPO</t>
+    <t>JPS-GL-BRC-PPO</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -440,7 +440,7 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -468,7 +468,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -496,7 +496,7 @@
         <v>64</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -524,7 +524,7 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -552,7 +552,7 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -580,7 +580,7 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -608,7 +608,7 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -636,7 +636,7 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
@@ -664,7 +664,7 @@
         <v>16</v>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -692,7 +692,7 @@
         <v>32</v>
       </c>
       <c r="C21">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -720,7 +720,7 @@
         <v>64</v>
       </c>
       <c r="C23">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -748,7 +748,7 @@
         <v>128</v>
       </c>
       <c r="C25">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -776,7 +776,7 @@
         <v>16</v>
       </c>
       <c r="C27">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
@@ -804,7 +804,7 @@
         <v>32</v>
       </c>
       <c r="C29">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
@@ -832,7 +832,7 @@
         <v>64</v>
       </c>
       <c r="C31">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
         <v>8</v>
@@ -860,7 +860,7 @@
         <v>128</v>
       </c>
       <c r="C33">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
@@ -888,7 +888,7 @@
         <v>16</v>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -916,7 +916,7 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -944,7 +944,7 @@
         <v>64</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -972,7 +972,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Open.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Open.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="13">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -31,7 +31,16 @@
     <t>A*</t>
   </si>
   <si>
-    <t>JPS-GL-BRC-PPO</t>
+    <t>BRC</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>JPS</t>
+  </si>
+  <si>
+    <t>PPO</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -401,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -440,7 +449,7 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -448,13 +457,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -462,13 +471,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -476,13 +485,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -490,13 +499,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -504,13 +513,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>379</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -518,13 +527,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -532,30 +541,30 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C10">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -563,13 +572,13 @@
         <v>4</v>
       </c>
       <c r="B12">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C12">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -577,125 +586,125 @@
         <v>5</v>
       </c>
       <c r="B13">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C13">
-        <v>13</v>
+        <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B14">
         <v>64</v>
       </c>
       <c r="C14">
-        <v>160</v>
+        <v>326</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>64</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B16">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C16">
-        <v>362</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17">
         <v>128</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>379</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C18">
-        <v>13</v>
+        <v>643</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>739</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B20">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C20">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>379</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -703,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B22">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -717,125 +726,125 @@
         <v>5</v>
       </c>
       <c r="B23">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B24">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>266</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B25">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B26">
         <v>16</v>
       </c>
       <c r="C26">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>32</v>
       </c>
       <c r="C28">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>32</v>
       </c>
       <c r="C29">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B30">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C30">
-        <v>352</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B31">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C31">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -843,13 +852,13 @@
         <v>4</v>
       </c>
       <c r="B32">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C32">
-        <v>873</v>
+        <v>160</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -857,24 +866,24 @@
         <v>5</v>
       </c>
       <c r="B33">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C33">
-        <v>17</v>
+        <v>331</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B34">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C34">
-        <v>73</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -882,13 +891,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -896,13 +905,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B36">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C36">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -910,13 +919,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>362</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -924,13 +933,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B38">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C38">
-        <v>578</v>
+        <v>836</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -938,13 +947,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B39">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>554</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -952,13 +961,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B40">
         <v>128</v>
       </c>
       <c r="C40">
-        <v>1281</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
@@ -966,16 +975,856 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B41">
         <v>128</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>362</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42">
+        <v>16</v>
+      </c>
+      <c r="C42">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44">
+        <v>16</v>
+      </c>
+      <c r="C44">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45">
+        <v>16</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46">
+        <v>16</v>
+      </c>
+      <c r="C46">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>32</v>
+      </c>
+      <c r="C47">
+        <v>44</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48">
+        <v>32</v>
+      </c>
+      <c r="C48">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49">
+        <v>32</v>
+      </c>
+      <c r="C49">
+        <v>55</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50">
+        <v>32</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51">
+        <v>32</v>
+      </c>
+      <c r="C51">
+        <v>44</v>
+      </c>
+      <c r="D51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>64</v>
+      </c>
+      <c r="C52">
+        <v>124</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53">
+        <v>64</v>
+      </c>
+      <c r="C53">
+        <v>229</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54">
+        <v>64</v>
+      </c>
+      <c r="C54">
+        <v>122</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55">
+        <v>64</v>
+      </c>
+      <c r="C55">
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>64</v>
+      </c>
+      <c r="C56">
+        <v>124</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>128</v>
+      </c>
+      <c r="C57">
+        <v>266</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58">
+        <v>128</v>
+      </c>
+      <c r="C58">
+        <v>544</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59">
+        <v>128</v>
+      </c>
+      <c r="C59">
+        <v>270</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60">
+        <v>128</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61">
+        <v>128</v>
+      </c>
+      <c r="C61">
+        <v>266</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62">
+        <v>16</v>
+      </c>
+      <c r="C62">
+        <v>34</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>16</v>
+      </c>
+      <c r="C63">
+        <v>38</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64">
+        <v>16</v>
+      </c>
+      <c r="C64">
+        <v>39</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65">
+        <v>16</v>
+      </c>
+      <c r="C65">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66">
+        <v>16</v>
+      </c>
+      <c r="C66">
+        <v>34</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67">
+        <v>32</v>
+      </c>
+      <c r="C67">
+        <v>114</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>32</v>
+      </c>
+      <c r="C68">
+        <v>91</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69">
+        <v>32</v>
+      </c>
+      <c r="C69">
+        <v>102</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70">
+        <v>32</v>
+      </c>
+      <c r="C70">
+        <v>20</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71">
+        <v>32</v>
+      </c>
+      <c r="C71">
+        <v>114</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72">
+        <v>64</v>
+      </c>
+      <c r="C72">
+        <v>352</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>64</v>
+      </c>
+      <c r="C73">
+        <v>230</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74">
+        <v>64</v>
+      </c>
+      <c r="C74">
+        <v>240</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75">
+        <v>64</v>
+      </c>
+      <c r="C75">
+        <v>25</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76">
+        <v>64</v>
+      </c>
+      <c r="C76">
+        <v>352</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77">
+        <v>128</v>
+      </c>
+      <c r="C77">
+        <v>873</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78">
+        <v>128</v>
+      </c>
+      <c r="C78">
+        <v>625</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>128</v>
+      </c>
+      <c r="C79">
+        <v>540</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80">
+        <v>128</v>
+      </c>
+      <c r="C80">
+        <v>22</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81">
+        <v>128</v>
+      </c>
+      <c r="C81">
+        <v>873</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82">
+        <v>16</v>
+      </c>
+      <c r="C82">
+        <v>73</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83">
+        <v>16</v>
+      </c>
+      <c r="C83">
+        <v>42</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>71</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85">
+        <v>16</v>
+      </c>
+      <c r="C85">
+        <v>11</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86">
+        <v>16</v>
+      </c>
+      <c r="C86">
+        <v>73</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87">
+        <v>32</v>
+      </c>
+      <c r="C87">
+        <v>252</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88">
+        <v>32</v>
+      </c>
+      <c r="C88">
+        <v>104</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>32</v>
+      </c>
+      <c r="C89">
+        <v>197</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90">
+        <v>32</v>
+      </c>
+      <c r="C90">
+        <v>10</v>
+      </c>
+      <c r="D90" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91">
+        <v>32</v>
+      </c>
+      <c r="C91">
+        <v>252</v>
+      </c>
+      <c r="D91" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92">
+        <v>64</v>
+      </c>
+      <c r="C92">
+        <v>578</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93">
+        <v>64</v>
+      </c>
+      <c r="C93">
+        <v>292</v>
+      </c>
+      <c r="D93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94">
+        <v>64</v>
+      </c>
+      <c r="C94">
+        <v>419</v>
+      </c>
+      <c r="D94" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95">
+        <v>64</v>
+      </c>
+      <c r="C95">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96">
+        <v>64</v>
+      </c>
+      <c r="C96">
+        <v>578</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97">
+        <v>128</v>
+      </c>
+      <c r="C97">
+        <v>1281</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98">
+        <v>128</v>
+      </c>
+      <c r="C98">
+        <v>614</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99">
+        <v>128</v>
+      </c>
+      <c r="C99">
+        <v>790</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100">
+        <v>128</v>
+      </c>
+      <c r="C100">
+        <v>12</v>
+      </c>
+      <c r="D100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101">
+        <v>128</v>
+      </c>
+      <c r="C101">
+        <v>1281</v>
+      </c>
+      <c r="D101" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Open.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Open.xlsx
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Open.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Open.xlsx
@@ -589,7 +589,7 @@
         <v>64</v>
       </c>
       <c r="C13">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -659,7 +659,7 @@
         <v>128</v>
       </c>
       <c r="C18">
-        <v>643</v>
+        <v>460</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>16</v>
       </c>
       <c r="C23">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -799,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -869,7 +869,7 @@
         <v>64</v>
       </c>
       <c r="C33">
-        <v>331</v>
+        <v>252</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -939,7 +939,7 @@
         <v>128</v>
       </c>
       <c r="C38">
-        <v>836</v>
+        <v>540</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C43">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>32</v>
       </c>
       <c r="C48">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -1149,7 +1149,7 @@
         <v>64</v>
       </c>
       <c r="C53">
-        <v>229</v>
+        <v>174</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -1219,7 +1219,7 @@
         <v>128</v>
       </c>
       <c r="C58">
-        <v>544</v>
+        <v>417</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -1429,7 +1429,7 @@
         <v>64</v>
       </c>
       <c r="C73">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -1499,7 +1499,7 @@
         <v>128</v>
       </c>
       <c r="C78">
-        <v>625</v>
+        <v>488</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -1569,7 +1569,7 @@
         <v>16</v>
       </c>
       <c r="C83">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D83" t="s">
         <v>12</v>
@@ -1639,7 +1639,7 @@
         <v>32</v>
       </c>
       <c r="C88">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
@@ -1709,7 +1709,7 @@
         <v>64</v>
       </c>
       <c r="C93">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
@@ -1779,7 +1779,7 @@
         <v>128</v>
       </c>
       <c r="C98">
-        <v>614</v>
+        <v>476</v>
       </c>
       <c r="D98" t="s">
         <v>12</v>
